--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.22109767464355</v>
+        <v>7.510928372129578</v>
       </c>
       <c r="D2" t="n">
-        <v>46.04030223926629</v>
+        <v>7.481549113880773</v>
       </c>
       <c r="E2" t="n">
-        <v>5.276604250882793</v>
+        <v>0.8574481907684539</v>
       </c>
       <c r="F2" t="n">
-        <v>6.334921550120315</v>
+        <v>1.029424751894551</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.82930725110101</v>
+        <v>5.334762428303914</v>
       </c>
       <c r="D3" t="n">
-        <v>32.22522962587724</v>
+        <v>5.236599814205052</v>
       </c>
       <c r="E3" t="n">
-        <v>5.276604250882793</v>
+        <v>0.8574481907684539</v>
       </c>
       <c r="F3" t="n">
-        <v>6.334921550120315</v>
+        <v>1.029424751894551</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.5042445434492</v>
+        <v>6.256939738310495</v>
       </c>
       <c r="D4" t="n">
-        <v>37.86867472407698</v>
+        <v>6.15365964266251</v>
       </c>
       <c r="E4" t="n">
-        <v>5.276604250882793</v>
+        <v>0.8574481907684539</v>
       </c>
       <c r="F4" t="n">
-        <v>6.334921550120315</v>
+        <v>1.029424751894551</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.99845649558935</v>
+        <v>6.174749180533269</v>
       </c>
       <c r="D5" t="n">
-        <v>36.85212015164865</v>
+        <v>5.988469524642905</v>
       </c>
       <c r="E5" t="n">
-        <v>5.276604250882793</v>
+        <v>0.8574481907684539</v>
       </c>
       <c r="F5" t="n">
-        <v>6.334921550120315</v>
+        <v>1.029424751894551</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.73102686218462</v>
+        <v>6.293791865105001</v>
       </c>
       <c r="D6" t="n">
-        <v>29.22984001244494</v>
+        <v>4.749849002022303</v>
       </c>
       <c r="E6" t="n">
-        <v>5.276604250882793</v>
+        <v>0.8574481907684539</v>
       </c>
       <c r="F6" t="n">
-        <v>6.334921550120315</v>
+        <v>1.029424751894551</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.38246970233548</v>
+        <v>7.862151326629515</v>
       </c>
       <c r="D7" t="n">
-        <v>26.8519883037301</v>
+        <v>4.363448099356141</v>
       </c>
       <c r="E7" t="n">
-        <v>5.276604250882793</v>
+        <v>0.8574481907684539</v>
       </c>
       <c r="F7" t="n">
-        <v>6.334921550120315</v>
+        <v>1.029424751894551</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
